--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_157_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_157_R16.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.630100000000001</v>
+        <v>9.0092</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0773</v>
+        <v>2.8597</v>
       </c>
       <c r="F2" t="n">
-        <v>6.5528</v>
+        <v>6.1495</v>
       </c>
       <c r="G2" t="n">
         <v>9.1044</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2574</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8962</v>
+        <v>-0.1138</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1536</v>
+        <v>0.7503</v>
       </c>
       <c r="V2" t="n">
         <v>1.3558</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2021</v>
+        <v>6.1338</v>
       </c>
       <c r="E3" t="n">
-        <v>1.13</v>
+        <v>2.8773</v>
       </c>
       <c r="F3" t="n">
-        <v>5.0721</v>
+        <v>3.2564</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9192</v>
+        <v>5.5166</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8045</v>
+        <v>2.7227</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1147</v>
+        <v>2.7939</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1111</v>
+        <v>3.0579</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6757</v>
+        <v>0.6288</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4354</v>
+        <v>2.4291</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8081</v>
+        <v>2.4587</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1288</v>
+        <v>2.094</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6793</v>
+        <v>0.3648</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.216</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0395</v>
+        <v>0.0514</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1765</v>
+        <v>0.0143</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7886</v>
+        <v>-1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8568</v>
+        <v>5.436</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5667</v>
+        <v>0.9688</v>
       </c>
       <c r="F4" t="n">
-        <v>3.29</v>
+        <v>4.4672</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5166</v>
+        <v>3.9192</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7227</v>
+        <v>1.8045</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7939</v>
+        <v>2.1147</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0579</v>
+        <v>2.1111</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6288</v>
+        <v>0.6757</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4291</v>
+        <v>1.4354</v>
       </c>
       <c r="M4" t="n">
-        <v>2.4587</v>
+        <v>1.8081</v>
       </c>
       <c r="N4" t="n">
-        <v>2.094</v>
+        <v>1.1288</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3648</v>
+        <v>0.6793</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2113</v>
+        <v>0.4499</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2592</v>
+        <v>-0.1217</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0479</v>
+        <v>0.5715</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8148</v>
+        <v>2.7221</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2324</v>
+        <v>0.0781</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0473</v>
+        <v>2.644</v>
       </c>
       <c r="G5" t="n">
         <v>1.9793</v>
@@ -844,13 +844,13 @@
         <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3717</v>
+        <v>0.279</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8215</v>
+        <v>-0.5109</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1931</v>
+        <v>0.7899</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0728</v>
+        <v>0.7419</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9003</v>
+        <v>-1.5897</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8275</v>
+        <v>2.3316</v>
       </c>
       <c r="G6" t="n">
         <v>1.2969</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3544</v>
+        <v>-0.5397</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9709</v>
+        <v>-0.6603</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3835</v>
+        <v>0.1206</v>
       </c>
       <c r="V6" t="n">
         <v>1.6083</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2377</v>
+        <v>0.4027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7271</v>
+        <v>-0.0194</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4893</v>
+        <v>0.4221</v>
       </c>
       <c r="G7" t="n">
         <v>0.676</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3776</v>
+        <v>-0.7371</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8215</v>
+        <v>-0.1138</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5561</v>
+        <v>-0.6234</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7187</v>
+        <v>-0.3814</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1598</v>
+        <v>0.6103</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4411</v>
+        <v>-0.9917</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1573</v>
+        <v>4.0131</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-1.0527</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>5.0658</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.43</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1573</v>
+        <v>0.0031</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.6227</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.6258</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1598</v>
+        <v>-5.1029</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-6.0307</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2838</v>
+        <v>-0.3637</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.5856</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2838</v>
+        <v>0.2219</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9533</v>
+        <v>-0.8468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3744</v>
+        <v>-0.446</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3277</v>
+        <v>-0.4008</v>
       </c>
       <c r="G9" t="n">
-        <v>4.0131</v>
+        <v>0.3046</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0527</v>
+        <v>-0.4249</v>
       </c>
       <c r="I9" t="n">
-        <v>5.0658</v>
+        <v>0.7294</v>
       </c>
       <c r="J9" t="n">
-        <v>4.01</v>
+        <v>0.1082</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.43</v>
+        <v>-0.5175</v>
       </c>
       <c r="L9" t="n">
-        <v>4.44</v>
+        <v>0.6257</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0031</v>
+        <v>0.1963</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6227</v>
+        <v>0.0926</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6258</v>
+        <v>0.1038</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.1029</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0307</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9357</v>
+        <v>-0.8472</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>-0.5542</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1142</v>
+        <v>-0.293</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1664</v>
+        <v>-0.8531</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5639</v>
+        <v>-1.1598</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6025</v>
+        <v>0.3066</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3046</v>
+        <v>0.1573</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4249</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7294</v>
+        <v>0.1573</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1082</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5175</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6257</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1963</v>
+        <v>0.1573</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0926</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1038</v>
+        <v>0.1573</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1668</v>
+        <v>0.1494</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4946</v>
+        <v>0.1494</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2471</v>
+        <v>-2.169</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7915</v>
+        <v>-0.8134</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5444</v>
+        <v>-1.3556</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4036</v>
+        <v>-0.5389</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0314</v>
+        <v>-0.8368</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.435</v>
+        <v>0.2978</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4146</v>
+        <v>-1.2502</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6148</v>
+        <v>-1.287</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7998</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" t="n">
-        <v>1.011</v>
+        <v>0.7113</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6462</v>
+        <v>0.4502</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3648</v>
+        <v>0.261</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4607</v>
+        <v>0.3725</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1745</v>
+        <v>0.295</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7139</v>
+        <v>0.0775</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6083</v>
+        <v>-2.0026</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2863</v>
+        <v>-2.7304</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6955</v>
+        <v>-3.4428</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5908</v>
+        <v>0.7125</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5389</v>
+        <v>-0.4036</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8368</v>
+        <v>0.0314</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2978</v>
+        <v>-0.435</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2502</v>
+        <v>-1.4146</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.287</v>
+        <v>-0.6148</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0368</v>
+        <v>-0.7998</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7113</v>
+        <v>1.011</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4502</v>
+        <v>0.6462</v>
       </c>
       <c r="O12" t="n">
-        <v>0.261</v>
+        <v>0.3648</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2552</v>
+        <v>-0.0226</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4129</v>
+        <v>0.5232</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1577</v>
+        <v>-0.5458</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0026</v>
+        <v>-1.6083</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9005</v>
+        <v>-4.1707</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0175</v>
+        <v>-1.4894</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.883</v>
+        <v>-2.6813</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1361</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5298</v>
+        <v>-0.8</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0351</v>
+        <v>-0.507</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4665</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.921</v>
+        <v>13.2943</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.9396</v>
+        <v>-1.5663</v>
       </c>
       <c r="F14" t="n">
         <v>14.8605</v>
@@ -1534,10 +1534,10 @@
         <v>8.3581</v>
       </c>
       <c r="O14" t="n">
-        <v>4.434200000000001</v>
+        <v>4.4342</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.798799999999999</v>
+        <v>-5.7988</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.3965</v>
@@ -1546,13 +1546,13 @@
         <v>11.5978</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7308</v>
+        <v>-1.3572</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.6711</v>
+        <v>-2.2977</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9402999999999999</v>
+        <v>0.9402000000000006</v>
       </c>
       <c r="V14" t="n">
         <v>-3.438</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4206</v>
+        <v>3.9089</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6774</v>
+        <v>2.0313</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7431</v>
+        <v>1.8776</v>
       </c>
       <c r="G15" t="n">
         <v>1.5085</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3585</v>
+        <v>0.1298</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3804</v>
+        <v>0.5149</v>
       </c>
       <c r="V15" t="n">
         <v>0.6468</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1407</v>
+        <v>1.5789</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5429</v>
+        <v>-1.0711</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6836</v>
+        <v>2.65</v>
       </c>
       <c r="G16" t="n">
         <v>-5.0231</v>
@@ -1702,13 +1702,13 @@
         <v>3.2473</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3905</v>
+        <v>0.8287</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4516</v>
+        <v>0.0202</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8421</v>
+        <v>0.8085</v>
       </c>
       <c r="V16" t="n">
         <v>5.0774</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0747</v>
+        <v>0.3518</v>
       </c>
       <c r="E17" t="n">
-        <v>0.949</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1256</v>
+        <v>-0.4793</v>
       </c>
       <c r="G17" t="n">
         <v>0.2543</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4286</v>
+        <v>0.7057</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0114</v>
+        <v>-0.1294</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>0.8351</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7117</v>
+        <v>-0.375</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07439999999999999</v>
+        <v>0.1615</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6373</v>
+        <v>-0.5365</v>
       </c>
       <c r="G18" t="n">
         <v>0.7648</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.778</v>
+        <v>-0.4413</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2161</v>
+        <v>0.0198</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5619</v>
+        <v>-0.461</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9304</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3289</v>
+        <v>-1.6574</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0754</v>
+        <v>0.9724</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7464</v>
+        <v>-2.6297</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.2863</v>
+        <v>-2.5669</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.4432</v>
+        <v>-0.4959</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8431</v>
+        <v>-2.071</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.1648</v>
+        <v>-0.5409</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.1648</v>
+        <v>-0.5777</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1215</v>
+        <v>-2.026</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7217</v>
+        <v>0.0818</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8431</v>
+        <v>-2.1078</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7976</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5534</v>
+        <v>0.2245</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2443</v>
+        <v>0.6671</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1285</v>
+        <v>-2.6429</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7365</v>
+        <v>-4.2549</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.865</v>
+        <v>1.612</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5669</v>
+        <v>-5.2863</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4959</v>
+        <v>-4.4432</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.071</v>
+        <v>-0.8431</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5409</v>
+        <v>-5.1648</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5777</v>
+        <v>-5.1648</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.026</v>
+        <v>-0.1215</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0818</v>
+        <v>0.7217</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1078</v>
+        <v>-0.8431</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4204</v>
+        <v>0.4837</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0114</v>
+        <v>0.3738</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4318</v>
+        <v>0.1098</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6805</v>
+        <v>0.5361</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.3584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9461</v>
+        <v>-3.1104</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8907</v>
+        <v>-2.6233</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9446</v>
+        <v>-0.4871</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1613</v>
+        <v>-4.3212</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.2884</v>
+        <v>1.3637</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1271</v>
+        <v>-5.6849</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1651</v>
+        <v>-2.7487</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.8743</v>
+        <v>1.1462</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7092000000000001</v>
+        <v>-3.8949</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0039</v>
+        <v>-1.5725</v>
       </c>
       <c r="N21" t="n">
-        <v>0.586</v>
+        <v>0.2175</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5821</v>
+        <v>-1.79</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4266</v>
+        <v>-0.163</v>
       </c>
       <c r="T21" t="n">
-        <v>0.13</v>
+        <v>0.0712</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2965</v>
+        <v>-0.2341</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2525</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3121</v>
+        <v>-3.5859</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6233</v>
+        <v>-4.3625</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6888</v>
+        <v>0.7766</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3212</v>
+        <v>-3.1613</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3637</v>
+        <v>-3.2884</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.6849</v>
+        <v>0.1271</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.7487</v>
+        <v>-3.1651</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1462</v>
+        <v>-3.8743</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.8949</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5725</v>
+        <v>0.0039</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2175</v>
+        <v>0.586</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.79</v>
+        <v>-0.5821</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3646</v>
+        <v>-0.2133</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0712</v>
+        <v>-0.3418</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4358</v>
+        <v>0.1285</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.2525</v>
       </c>
       <c r="W22" t="n">
-        <v>1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7374</v>
+        <v>-3.6201</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6922</v>
+        <v>-3.8101</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0452</v>
+        <v>0.1901</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2507</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1103</v>
+        <v>0.007</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2434</v>
+        <v>-0.3613</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1331</v>
+        <v>0.3684</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3922</v>
+        <v>-3.7689</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3246</v>
+        <v>-2.7348</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0676</v>
+        <v>-1.034</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8068</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1215</v>
+        <v>-0.4982</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0218</v>
+        <v>-0.4321</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0997</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.9209</v>
+        <v>-12.921</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.8606</v>
+        <v>-14.8604</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9394</v>
+        <v>1.9397</v>
       </c>
       <c r="G25" t="n">
         <v>-23.8887</v>
@@ -2404,13 +2404,13 @@
         <v>17.3965</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7308</v>
+        <v>1.7307</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9400000000000004</v>
+        <v>-0.9401999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6708</v>
+        <v>2.6711</v>
       </c>
       <c r="V25" t="n">
         <v>3.437999999999999</v>
